--- a/p_marker_DEHII_EC3.8.1.2_K01560/primer_dgp_dehII2_Supplementary.xlsx
+++ b/p_marker_DEHII_EC3.8.1.2_K01560/primer_dgp_dehII2_Supplementary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/PRIMERS/tesiR/4_3.1.8.2_K01560_ldex/primer_ldex/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/THESIS/p_marker_DEHII_EC3.8.1.2_K01560/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9509B72-C6B3-4C0E-B92B-CBA760415FC3}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1F178C9-C631-467D-88C9-52B01A769D5B}"/>
   <bookViews>
-    <workbookView xWindow="9518" yWindow="0" windowWidth="9765" windowHeight="11363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -462,10 +462,10 @@
       <c r="E3">
         <v>0.545319</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>243</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>34992</v>
       </c>
       <c r="H3" t="s">
@@ -488,10 +488,10 @@
       <c r="E4">
         <v>7.3550000000000004E-3</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>243</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>6561</v>
       </c>
       <c r="H4" t="s">
@@ -514,10 +514,10 @@
       <c r="E5">
         <v>0.21438599999999999</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>729</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>6561</v>
       </c>
       <c r="H5" t="s">
@@ -540,10 +540,10 @@
       <c r="E6">
         <v>0.45559699999999997</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>729</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>52488</v>
       </c>
       <c r="H6" t="s">
@@ -566,10 +566,10 @@
       <c r="E7">
         <v>0.33432000000000001</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>2187</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>78732</v>
       </c>
       <c r="H7" t="s">
